--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B2" t="n">
-        <v>56880</v>
+        <v>78847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R2" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,32 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B3" t="n">
-        <v>78847</v>
+        <v>56880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R3" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723802</v>
+        <v>128723818</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379682</v>
+        <v>379743</v>
       </c>
       <c r="R5" t="n">
-        <v>6858830</v>
+        <v>6858829</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723813</v>
+        <v>128723821</v>
       </c>
       <c r="B6" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379655</v>
+        <v>379664</v>
       </c>
       <c r="R6" t="n">
-        <v>6858399</v>
+        <v>6858437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1185,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723818</v>
+        <v>128723802</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379743</v>
+        <v>379682</v>
       </c>
       <c r="R7" t="n">
-        <v>6858829</v>
+        <v>6858830</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1303,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723821</v>
+        <v>128723813</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379664</v>
+        <v>379655</v>
       </c>
       <c r="R8" t="n">
-        <v>6858437</v>
+        <v>6858399</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128723819</v>
+        <v>128723822</v>
       </c>
       <c r="B9" t="n">
         <v>78846</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>379757</v>
+        <v>379655</v>
       </c>
       <c r="R9" t="n">
-        <v>6858565</v>
+        <v>6858399</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128723822</v>
+        <v>128723819</v>
       </c>
       <c r="B10" t="n">
         <v>78846</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>379655</v>
+        <v>379757</v>
       </c>
       <c r="R10" t="n">
-        <v>6858399</v>
+        <v>6858565</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723823</v>
+        <v>128723813</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379646</v>
+        <v>379655</v>
       </c>
       <c r="R4" t="n">
-        <v>6858382</v>
+        <v>6858399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723818</v>
+        <v>128723802</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379743</v>
+        <v>379682</v>
       </c>
       <c r="R5" t="n">
-        <v>6858829</v>
+        <v>6858830</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1087,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1106,7 +1105,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723821</v>
+        <v>128723823</v>
       </c>
       <c r="B6" t="n">
         <v>78846</v>
@@ -1141,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379664</v>
+        <v>379646</v>
       </c>
       <c r="R6" t="n">
-        <v>6858437</v>
+        <v>6858382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1175,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1185,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723802</v>
+        <v>128723818</v>
       </c>
       <c r="B7" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379682</v>
+        <v>379743</v>
       </c>
       <c r="R7" t="n">
-        <v>6858830</v>
+        <v>6858829</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1294,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,6 +1302,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723813</v>
+        <v>128723821</v>
       </c>
       <c r="B8" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379655</v>
+        <v>379664</v>
       </c>
       <c r="R8" t="n">
-        <v>6858399</v>
+        <v>6858437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B2" t="n">
-        <v>78847</v>
+        <v>56880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R2" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B3" t="n">
-        <v>56880</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R3" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723813</v>
+        <v>128723802</v>
       </c>
       <c r="B4" t="n">
-        <v>78847</v>
+        <v>79708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379655</v>
+        <v>379682</v>
       </c>
       <c r="R4" t="n">
-        <v>6858399</v>
+        <v>6858830</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723802</v>
+        <v>128723823</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1008,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379682</v>
+        <v>379646</v>
       </c>
       <c r="R5" t="n">
-        <v>6858830</v>
+        <v>6858382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1067,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1077,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723823</v>
+        <v>128723818</v>
       </c>
       <c r="B6" t="n">
         <v>78846</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379646</v>
+        <v>379743</v>
       </c>
       <c r="R6" t="n">
-        <v>6858382</v>
+        <v>6858829</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723818</v>
+        <v>128723821</v>
       </c>
       <c r="B7" t="n">
         <v>78846</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379743</v>
+        <v>379664</v>
       </c>
       <c r="R7" t="n">
-        <v>6858829</v>
+        <v>6858437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723821</v>
+        <v>128723813</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379664</v>
+        <v>379655</v>
       </c>
       <c r="R8" t="n">
-        <v>6858437</v>
+        <v>6858399</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1645,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128723817</v>
+        <v>128723807</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>97468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379836</v>
+        <v>379681</v>
       </c>
       <c r="R11" t="n">
-        <v>6858215</v>
+        <v>6858831</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,7 +1734,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1753,32 +1752,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128723807</v>
+        <v>128723817</v>
       </c>
       <c r="B12" t="n">
-        <v>97468</v>
+        <v>78846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>379681</v>
+        <v>379836</v>
       </c>
       <c r="R12" t="n">
-        <v>6858831</v>
+        <v>6858215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,6 +1841,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723802</v>
+        <v>128723823</v>
       </c>
       <c r="B4" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379682</v>
+        <v>379646</v>
       </c>
       <c r="R4" t="n">
-        <v>6858830</v>
+        <v>6858382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,6 +979,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723823</v>
+        <v>128723818</v>
       </c>
       <c r="B5" t="n">
         <v>78846</v>
@@ -1032,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379646</v>
+        <v>379743</v>
       </c>
       <c r="R5" t="n">
-        <v>6858382</v>
+        <v>6858829</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1077,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723818</v>
+        <v>128723802</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379743</v>
+        <v>379682</v>
       </c>
       <c r="R6" t="n">
-        <v>6858829</v>
+        <v>6858830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1185,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128723807</v>
+        <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>97468</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379681</v>
+        <v>379836</v>
       </c>
       <c r="R11" t="n">
-        <v>6858831</v>
+        <v>6858215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,6 +1734,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1752,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128723817</v>
+        <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>78846</v>
+        <v>97469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>379836</v>
+        <v>379681</v>
       </c>
       <c r="R12" t="n">
-        <v>6858215</v>
+        <v>6858831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1842,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723804</v>
       </c>
       <c r="B2" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128723815</v>
       </c>
       <c r="B3" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128723823</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128723818</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>128723802</v>
       </c>
       <c r="B6" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128723821</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>128723813</v>
       </c>
       <c r="B8" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128723822</v>
       </c>
       <c r="B9" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>128723819</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128723803</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128723814</v>
       </c>
       <c r="B14" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>128723820</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128723825</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>128723811</v>
       </c>
       <c r="B17" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>128723810</v>
       </c>
       <c r="B18" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128723827</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128723816</v>
       </c>
       <c r="B20" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128723812</v>
       </c>
       <c r="B21" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B2" t="n">
-        <v>56907</v>
+        <v>78874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R2" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,32 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B3" t="n">
-        <v>78874</v>
+        <v>56907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R3" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723815</v>
       </c>
       <c r="B2" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128723823</v>
       </c>
       <c r="B4" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128723818</v>
       </c>
       <c r="B5" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>128723802</v>
       </c>
       <c r="B6" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723821</v>
+        <v>128723813</v>
       </c>
       <c r="B7" t="n">
-        <v>78873</v>
+        <v>78878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379664</v>
+        <v>379655</v>
       </c>
       <c r="R7" t="n">
-        <v>6858437</v>
+        <v>6858399</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723813</v>
+        <v>128723821</v>
       </c>
       <c r="B8" t="n">
-        <v>78874</v>
+        <v>78877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379655</v>
+        <v>379664</v>
       </c>
       <c r="R8" t="n">
-        <v>6858399</v>
+        <v>6858437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,7 +1432,7 @@
         <v>128723822</v>
       </c>
       <c r="B9" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>128723819</v>
       </c>
       <c r="B10" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128723817</v>
+        <v>128723807</v>
       </c>
       <c r="B11" t="n">
-        <v>78873</v>
+        <v>97502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379836</v>
+        <v>379681</v>
       </c>
       <c r="R11" t="n">
-        <v>6858215</v>
+        <v>6858831</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,7 +1734,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1753,32 +1752,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128723807</v>
+        <v>128723817</v>
       </c>
       <c r="B12" t="n">
-        <v>97496</v>
+        <v>78877</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>379681</v>
+        <v>379836</v>
       </c>
       <c r="R12" t="n">
-        <v>6858831</v>
+        <v>6858215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,6 +1841,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>128723803</v>
       </c>
       <c r="B13" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128723814</v>
       </c>
       <c r="B14" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>128723820</v>
       </c>
       <c r="B15" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128723825</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>128723811</v>
       </c>
       <c r="B17" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>128723810</v>
       </c>
       <c r="B18" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128723827</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128723816</v>
       </c>
       <c r="B20" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128723812</v>
       </c>
       <c r="B21" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723802</v>
+        <v>128723821</v>
       </c>
       <c r="B6" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379682</v>
+        <v>379664</v>
       </c>
       <c r="R6" t="n">
-        <v>6858830</v>
+        <v>6858437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723813</v>
+        <v>128723802</v>
       </c>
       <c r="B7" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379655</v>
+        <v>379682</v>
       </c>
       <c r="R7" t="n">
-        <v>6858399</v>
+        <v>6858830</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1303,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723821</v>
+        <v>128723813</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379664</v>
+        <v>379655</v>
       </c>
       <c r="R8" t="n">
-        <v>6858437</v>
+        <v>6858399</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1645,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128723807</v>
+        <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>97502</v>
+        <v>78877</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379681</v>
+        <v>379836</v>
       </c>
       <c r="R11" t="n">
-        <v>6858831</v>
+        <v>6858215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,6 +1734,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1752,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128723817</v>
+        <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>78877</v>
+        <v>97509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>379836</v>
+        <v>379681</v>
       </c>
       <c r="R12" t="n">
-        <v>6858215</v>
+        <v>6858831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1842,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B2" t="n">
-        <v>78878</v>
+        <v>56907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R2" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B3" t="n">
-        <v>56907</v>
+        <v>78878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R3" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723821</v>
+        <v>128723802</v>
       </c>
       <c r="B6" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379664</v>
+        <v>379682</v>
       </c>
       <c r="R6" t="n">
-        <v>6858437</v>
+        <v>6858830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1214,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723802</v>
+        <v>128723821</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379682</v>
+        <v>379664</v>
       </c>
       <c r="R7" t="n">
-        <v>6858830</v>
+        <v>6858437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1294,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,6 +1302,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723823</v>
+        <v>128723813</v>
       </c>
       <c r="B4" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379646</v>
+        <v>379655</v>
       </c>
       <c r="R4" t="n">
-        <v>6858382</v>
+        <v>6858399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723818</v>
+        <v>128723823</v>
       </c>
       <c r="B5" t="n">
         <v>78877</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379743</v>
+        <v>379646</v>
       </c>
       <c r="R5" t="n">
-        <v>6858829</v>
+        <v>6858382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723802</v>
+        <v>128723818</v>
       </c>
       <c r="B6" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379682</v>
+        <v>379743</v>
       </c>
       <c r="R6" t="n">
-        <v>6858830</v>
+        <v>6858829</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723821</v>
+        <v>128723802</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379664</v>
+        <v>379682</v>
       </c>
       <c r="R7" t="n">
-        <v>6858437</v>
+        <v>6858830</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1303,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723813</v>
+        <v>128723821</v>
       </c>
       <c r="B8" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379655</v>
+        <v>379664</v>
       </c>
       <c r="R8" t="n">
-        <v>6858399</v>
+        <v>6858437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B2" t="n">
-        <v>56907</v>
+        <v>78882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R2" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,32 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B3" t="n">
-        <v>78878</v>
+        <v>56910</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R3" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723813</v>
+        <v>128723823</v>
       </c>
       <c r="B4" t="n">
-        <v>78878</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379655</v>
+        <v>379646</v>
       </c>
       <c r="R4" t="n">
-        <v>6858399</v>
+        <v>6858382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723823</v>
+        <v>128723813</v>
       </c>
       <c r="B5" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379646</v>
+        <v>379655</v>
       </c>
       <c r="R5" t="n">
-        <v>6858382</v>
+        <v>6858399</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1109,7 @@
         <v>128723818</v>
       </c>
       <c r="B6" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>128723802</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>128723821</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128723822</v>
       </c>
       <c r="B9" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>128723819</v>
       </c>
       <c r="B10" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128723803</v>
       </c>
       <c r="B13" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128723814</v>
       </c>
       <c r="B14" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>128723820</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128723825</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>128723811</v>
       </c>
       <c r="B17" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>128723810</v>
       </c>
       <c r="B18" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128723827</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128723816</v>
       </c>
       <c r="B20" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128723812</v>
       </c>
       <c r="B21" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B2" t="n">
-        <v>78882</v>
+        <v>56910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R2" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B3" t="n">
-        <v>56910</v>
+        <v>78882</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R3" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723823</v>
+        <v>128723813</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379646</v>
+        <v>379655</v>
       </c>
       <c r="R4" t="n">
-        <v>6858382</v>
+        <v>6858399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723813</v>
+        <v>128723823</v>
       </c>
       <c r="B5" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379655</v>
+        <v>379646</v>
       </c>
       <c r="R5" t="n">
-        <v>6858399</v>
+        <v>6858382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1645,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128723817</v>
+        <v>128723807</v>
       </c>
       <c r="B11" t="n">
-        <v>78881</v>
+        <v>97513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379836</v>
+        <v>379681</v>
       </c>
       <c r="R11" t="n">
-        <v>6858215</v>
+        <v>6858831</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,7 +1734,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1753,32 +1752,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128723807</v>
+        <v>128723817</v>
       </c>
       <c r="B12" t="n">
-        <v>97513</v>
+        <v>78881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>379681</v>
+        <v>379836</v>
       </c>
       <c r="R12" t="n">
-        <v>6858831</v>
+        <v>6858215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,6 +1841,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723823</v>
+        <v>128723802</v>
       </c>
       <c r="B5" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379646</v>
+        <v>379682</v>
       </c>
       <c r="R5" t="n">
-        <v>6858382</v>
+        <v>6858830</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1087,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1106,7 +1105,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723818</v>
+        <v>128723821</v>
       </c>
       <c r="B6" t="n">
         <v>78881</v>
@@ -1141,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379743</v>
+        <v>379664</v>
       </c>
       <c r="R6" t="n">
-        <v>6858829</v>
+        <v>6858437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1175,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1185,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723802</v>
+        <v>128723818</v>
       </c>
       <c r="B7" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379682</v>
+        <v>379743</v>
       </c>
       <c r="R7" t="n">
-        <v>6858830</v>
+        <v>6858829</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1294,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,6 +1302,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723821</v>
+        <v>128723823</v>
       </c>
       <c r="B8" t="n">
         <v>78881</v>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379664</v>
+        <v>379646</v>
       </c>
       <c r="R8" t="n">
-        <v>6858437</v>
+        <v>6858382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1645,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128723807</v>
+        <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>97513</v>
+        <v>78881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379681</v>
+        <v>379836</v>
       </c>
       <c r="R11" t="n">
-        <v>6858831</v>
+        <v>6858215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,6 +1734,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1752,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128723817</v>
+        <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>78881</v>
+        <v>97513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>379836</v>
+        <v>379681</v>
       </c>
       <c r="R12" t="n">
-        <v>6858215</v>
+        <v>6858831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1842,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723804</v>
       </c>
       <c r="B2" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128723815</v>
       </c>
       <c r="B3" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128723813</v>
       </c>
       <c r="B4" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723802</v>
+        <v>128723823</v>
       </c>
       <c r="B5" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379682</v>
+        <v>379646</v>
       </c>
       <c r="R5" t="n">
-        <v>6858830</v>
+        <v>6858382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723821</v>
+        <v>128723818</v>
       </c>
       <c r="B6" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379664</v>
+        <v>379743</v>
       </c>
       <c r="R6" t="n">
-        <v>6858437</v>
+        <v>6858829</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1185,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723818</v>
+        <v>128723821</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379743</v>
+        <v>379664</v>
       </c>
       <c r="R7" t="n">
-        <v>6858829</v>
+        <v>6858437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723823</v>
+        <v>128723802</v>
       </c>
       <c r="B8" t="n">
-        <v>78881</v>
+        <v>79648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379646</v>
+        <v>379682</v>
       </c>
       <c r="R8" t="n">
-        <v>6858382</v>
+        <v>6858830</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,7 +1411,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>128723822</v>
       </c>
       <c r="B9" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>128723819</v>
       </c>
       <c r="B10" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128723803</v>
       </c>
       <c r="B13" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128723814</v>
       </c>
       <c r="B14" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>128723820</v>
       </c>
       <c r="B15" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128723825</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>128723811</v>
       </c>
       <c r="B17" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>128723810</v>
       </c>
       <c r="B18" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128723827</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128723816</v>
       </c>
       <c r="B20" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128723812</v>
       </c>
       <c r="B21" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B2" t="n">
-        <v>56913</v>
+        <v>78792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R2" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,32 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>56913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R3" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723823</v>
+        <v>128723813</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379646</v>
+        <v>379655</v>
       </c>
       <c r="R4" t="n">
-        <v>6858382</v>
+        <v>6858399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723818</v>
+        <v>128723823</v>
       </c>
       <c r="B5" t="n">
         <v>78791</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379743</v>
+        <v>379646</v>
       </c>
       <c r="R5" t="n">
-        <v>6858829</v>
+        <v>6858382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723802</v>
+        <v>128723818</v>
       </c>
       <c r="B6" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379682</v>
+        <v>379743</v>
       </c>
       <c r="R6" t="n">
-        <v>6858830</v>
+        <v>6858829</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723821</v>
+        <v>128723802</v>
       </c>
       <c r="B7" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379664</v>
+        <v>379682</v>
       </c>
       <c r="R7" t="n">
-        <v>6858437</v>
+        <v>6858830</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1303,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723813</v>
+        <v>128723821</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379655</v>
+        <v>379664</v>
       </c>
       <c r="R8" t="n">
-        <v>6858399</v>
+        <v>6858437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1648,7 +1648,7 @@
         <v>128723807</v>
       </c>
       <c r="B11" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>56913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R2" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B3" t="n">
-        <v>56913</v>
+        <v>78793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R3" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,7 +893,7 @@
         <v>128723813</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128723823</v>
       </c>
       <c r="B5" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>128723818</v>
       </c>
       <c r="B6" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>128723802</v>
       </c>
       <c r="B7" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>128723821</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128723822</v>
       </c>
       <c r="B9" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>128723819</v>
       </c>
       <c r="B10" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128723807</v>
+        <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>97533</v>
+        <v>78792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379681</v>
+        <v>379836</v>
       </c>
       <c r="R11" t="n">
-        <v>6858831</v>
+        <v>6858215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,6 +1734,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1752,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128723817</v>
+        <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>78791</v>
+        <v>97536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>379836</v>
+        <v>379681</v>
       </c>
       <c r="R12" t="n">
-        <v>6858215</v>
+        <v>6858831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1842,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>128723803</v>
       </c>
       <c r="B13" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128723814</v>
       </c>
       <c r="B14" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>128723820</v>
       </c>
       <c r="B15" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128723825</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>128723811</v>
       </c>
       <c r="B17" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>128723810</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128723827</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128723816</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128723812</v>
       </c>
       <c r="B21" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B2" t="n">
-        <v>56913</v>
+        <v>78793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R2" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,32 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B3" t="n">
-        <v>78793</v>
+        <v>56913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R3" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723813</v>
+        <v>128723823</v>
       </c>
       <c r="B4" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379655</v>
+        <v>379646</v>
       </c>
       <c r="R4" t="n">
-        <v>6858399</v>
+        <v>6858382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723823</v>
+        <v>128723818</v>
       </c>
       <c r="B5" t="n">
         <v>78792</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379646</v>
+        <v>379743</v>
       </c>
       <c r="R5" t="n">
-        <v>6858382</v>
+        <v>6858829</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723818</v>
+        <v>128723802</v>
       </c>
       <c r="B6" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379743</v>
+        <v>379682</v>
       </c>
       <c r="R6" t="n">
-        <v>6858829</v>
+        <v>6858830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1214,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723802</v>
+        <v>128723821</v>
       </c>
       <c r="B7" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379682</v>
+        <v>379664</v>
       </c>
       <c r="R7" t="n">
-        <v>6858830</v>
+        <v>6858437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1294,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,6 +1302,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723821</v>
+        <v>128723813</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379664</v>
+        <v>379655</v>
       </c>
       <c r="R8" t="n">
-        <v>6858437</v>
+        <v>6858399</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128723815</v>
+        <v>128723804</v>
       </c>
       <c r="B2" t="n">
-        <v>78793</v>
+        <v>56913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379673</v>
+        <v>379678</v>
       </c>
       <c r="R2" t="n">
-        <v>6858285</v>
+        <v>6858744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128723804</v>
+        <v>128723815</v>
       </c>
       <c r="B3" t="n">
-        <v>56913</v>
+        <v>78793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379678</v>
+        <v>379673</v>
       </c>
       <c r="R3" t="n">
-        <v>6858744</v>
+        <v>6858285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -863,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128723817</v>
+        <v>128723807</v>
       </c>
       <c r="B11" t="n">
-        <v>78792</v>
+        <v>97536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379836</v>
+        <v>379681</v>
       </c>
       <c r="R11" t="n">
-        <v>6858215</v>
+        <v>6858831</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,7 +1734,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1753,32 +1752,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128723807</v>
+        <v>128723817</v>
       </c>
       <c r="B12" t="n">
-        <v>97536</v>
+        <v>78792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>379681</v>
+        <v>379836</v>
       </c>
       <c r="R12" t="n">
-        <v>6858831</v>
+        <v>6858215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,6 +1841,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723823</v>
+        <v>128723813</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379646</v>
+        <v>379655</v>
       </c>
       <c r="R4" t="n">
-        <v>6858382</v>
+        <v>6858399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723818</v>
+        <v>128723823</v>
       </c>
       <c r="B5" t="n">
         <v>78792</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379743</v>
+        <v>379646</v>
       </c>
       <c r="R5" t="n">
-        <v>6858829</v>
+        <v>6858382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723802</v>
+        <v>128723818</v>
       </c>
       <c r="B6" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379682</v>
+        <v>379743</v>
       </c>
       <c r="R6" t="n">
-        <v>6858830</v>
+        <v>6858829</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723821</v>
+        <v>128723802</v>
       </c>
       <c r="B7" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379664</v>
+        <v>379682</v>
       </c>
       <c r="R7" t="n">
-        <v>6858437</v>
+        <v>6858830</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1303,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723813</v>
+        <v>128723821</v>
       </c>
       <c r="B8" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379655</v>
+        <v>379664</v>
       </c>
       <c r="R8" t="n">
-        <v>6858399</v>
+        <v>6858437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1645,32 +1645,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128723807</v>
+        <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>97536</v>
+        <v>78792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379681</v>
+        <v>379836</v>
       </c>
       <c r="R11" t="n">
-        <v>6858831</v>
+        <v>6858215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,6 +1734,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1752,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128723817</v>
+        <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>78792</v>
+        <v>97536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>379836</v>
+        <v>379681</v>
       </c>
       <c r="R12" t="n">
-        <v>6858215</v>
+        <v>6858831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1842,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723804</v>
       </c>
       <c r="B2" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128723815</v>
       </c>
       <c r="B3" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128723813</v>
+        <v>128723823</v>
       </c>
       <c r="B4" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379655</v>
+        <v>379646</v>
       </c>
       <c r="R4" t="n">
-        <v>6858399</v>
+        <v>6858382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128723823</v>
+        <v>128723818</v>
       </c>
       <c r="B5" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379646</v>
+        <v>379743</v>
       </c>
       <c r="R5" t="n">
-        <v>6858382</v>
+        <v>6858829</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128723818</v>
+        <v>128723802</v>
       </c>
       <c r="B6" t="n">
-        <v>78792</v>
+        <v>79658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379743</v>
+        <v>379682</v>
       </c>
       <c r="R6" t="n">
-        <v>6858829</v>
+        <v>6858830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1214,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128723802</v>
+        <v>128723821</v>
       </c>
       <c r="B7" t="n">
-        <v>79654</v>
+        <v>78796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379682</v>
+        <v>379664</v>
       </c>
       <c r="R7" t="n">
-        <v>6858830</v>
+        <v>6858437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1294,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,6 +1302,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128723821</v>
+        <v>128723813</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379664</v>
+        <v>379655</v>
       </c>
       <c r="R8" t="n">
-        <v>6858437</v>
+        <v>6858399</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,7 +1432,7 @@
         <v>128723822</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>128723819</v>
       </c>
       <c r="B10" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128723803</v>
       </c>
       <c r="B13" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128723814</v>
       </c>
       <c r="B14" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>128723820</v>
       </c>
       <c r="B15" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128723825</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>128723811</v>
       </c>
       <c r="B17" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>128723810</v>
       </c>
       <c r="B18" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128723827</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128723816</v>
       </c>
       <c r="B20" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128723812</v>
       </c>
       <c r="B21" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128723822</v>
+        <v>128723819</v>
       </c>
       <c r="B9" t="n">
         <v>78796</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>379655</v>
+        <v>379757</v>
       </c>
       <c r="R9" t="n">
-        <v>6858399</v>
+        <v>6858565</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128723819</v>
+        <v>128723822</v>
       </c>
       <c r="B10" t="n">
         <v>78796</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>379757</v>
+        <v>379655</v>
       </c>
       <c r="R10" t="n">
-        <v>6858565</v>
+        <v>6858399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128723804</v>
       </c>
       <c r="B2" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128723815</v>
       </c>
       <c r="B3" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128723823</v>
       </c>
       <c r="B4" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>128723818</v>
       </c>
       <c r="B5" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>128723802</v>
       </c>
       <c r="B6" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128723821</v>
       </c>
       <c r="B7" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>128723813</v>
       </c>
       <c r="B8" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128723819</v>
+        <v>128723822</v>
       </c>
       <c r="B9" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>379757</v>
+        <v>379655</v>
       </c>
       <c r="R9" t="n">
-        <v>6858565</v>
+        <v>6858399</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128723822</v>
+        <v>128723819</v>
       </c>
       <c r="B10" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>379655</v>
+        <v>379757</v>
       </c>
       <c r="R10" t="n">
-        <v>6858399</v>
+        <v>6858565</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,7 +1648,7 @@
         <v>128723817</v>
       </c>
       <c r="B11" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>128723807</v>
       </c>
       <c r="B12" t="n">
-        <v>97546</v>
+        <v>97555</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128723803</v>
       </c>
       <c r="B13" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128723814</v>
       </c>
       <c r="B14" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>128723820</v>
       </c>
       <c r="B15" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>128723825</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>128723811</v>
       </c>
       <c r="B17" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>128723810</v>
       </c>
       <c r="B18" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128723827</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128723816</v>
       </c>
       <c r="B20" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128723812</v>
       </c>
       <c r="B21" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40417-2025 artfynd.xlsx
+++ b/artfynd/A 40417-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723825</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723827</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723817</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723818</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723819</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723820</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723821</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723822</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723823</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1749,6 +1799,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723801</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1856,6 +1911,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723802</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1963,6 +2023,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723803</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2070,6 +2135,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723804</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2177,6 +2247,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723807</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2285,6 +2360,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723809</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2393,6 +2473,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723810</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2501,6 +2586,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723811</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2609,6 +2699,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723812</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2717,6 +2812,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723813</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2825,6 +2925,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723814</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2933,6 +3038,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723815</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3041,6 +3151,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723816</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3149,8 +3264,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128723806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>